--- a/document-parsing/evaluate/paddleocr-vl_半导体场景模拟数据_解析benchmark评分.xlsx
+++ b/document-parsing/evaluate/paddleocr-vl_半导体场景模拟数据_解析benchmark评分.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6637225871e5480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="2" r:id="R6fdce543f641488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimension Details" sheetId="3" r:id="Rcf2e4613411446b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R7aa02a474e644fd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores" sheetId="2" r:id="Rb36ac055f4924816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dimension Details" sheetId="3" r:id="R00686898f5794ab1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -122,7 +122,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1"/>
@@ -187,6 +187,9 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -466,11 +469,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
-    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="52" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.670000076293945" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="13.890000343322754" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10.329999923706055" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="9.109999656677246" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -483,7 +486,7 @@
       <x:c r="D1" s="2"/>
     </x:row>
     <x:row r="2"/>
-    <x:row r="3" ht="15" hidden="0" customHeight="1">
+    <x:row r="3" ht="32" hidden="0" customHeight="1">
       <x:c r="A3" s="15" t="str">
         <x:v>Product</x:v>
       </x:c>
@@ -497,10 +500,10 @@
         <x:v>Contributing files</x:v>
       </x:c>
       <x:c r="F3" s="21" t="str">
-        <x:v>F1 equal avg</x:v>
+        <x:v>Per-dimension F1 avg across files</x:v>
       </x:c>
       <x:c r="G3" s="21" t="str">
-        <x:v>F1 count-weighted avg</x:v>
+        <x:v>Per-dimension F1 weighted by all elements</x:v>
       </x:c>
       <x:c r="H3" s="21" t="str">
         <x:v>Total count</x:v>
@@ -575,9 +578,9 @@
         <x:v>52</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="15" t="str">
-        <x:v>Avg equal-weight score across files</x:v>
+    <x:row r="7" ht="30" hidden="0" customHeight="1">
+      <x:c r="A7" s="25" t="str">
+        <x:v>50-file avg of per-file dimension-equal scores</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
         <x:v>0.5855667428571428</x:v>
@@ -598,9 +601,9 @@
         <x:v>1671</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="58" hidden="0" customHeight="1">
-      <x:c r="A8" s="15" t="str">
-        <x:v>Avg count-weighted score across files</x:v>
+    <x:row r="8" ht="30" hidden="0" customHeight="1">
+      <x:c r="A8" s="25" t="str">
+        <x:v>50-file avg of per-file element-count-weighted scores</x:v>
       </x:c>
       <x:c r="B8" s="17" t="n">
         <x:v>0.7048128339376993</x:v>
@@ -726,15 +729,15 @@
     <x:col min="22" max="22" width="16" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="17.670000076293945" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="19" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="18.219999313354492" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="20.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="36" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="36" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="16.889999389648438" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="60" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="60" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="60" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="32" hidden="0" customHeight="1">
       <x:c r="A1" s="21" t="str">
         <x:v>case_name</x:v>
       </x:c>
@@ -808,10 +811,10 @@
         <x:v>title_hierarchy_count</x:v>
       </x:c>
       <x:c r="Y1" s="21" t="str">
-        <x:v>equal_weight_score</x:v>
+        <x:v>per_file_dimension_equal_score</x:v>
       </x:c>
       <x:c r="Z1" s="21" t="str">
-        <x:v>count_weighted_score</x:v>
+        <x:v>per_file_element_count_weighted_score</x:v>
       </x:c>
       <x:c r="AA1" s="21" t="str">
         <x:v>tool_overall_score</x:v>
@@ -4443,7 +4446,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4706de6b2eb84ab3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8958ab248b334ccd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19757,7 +19760,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc87eed09fa3042c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1397a39c9847e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>